--- a/HL-MCK_Fake_Fingerprint_BaoCao_v4.xlsx
+++ b/HL-MCK_Fake_Fingerprint_BaoCao_v4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DOAN\SEP490_G55_Automation_Antidetect_Browser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8E715D86-4B11-44B8-8BE0-72C52AF031C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6D19320-7EE7-4DCA-9427-84A34CBAC24E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Kien truc tong quan" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,6 @@
     <sheet name="6. Ly do fake &amp; So sanh" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -2136,7 +2135,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2272,20 +2271,21 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -2295,7 +2295,6 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -2606,14 +2605,14 @@
     <tabColor rgb="FF1F3864"/>
   </sheetPr>
   <dimension ref="A1:F23"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="98" customWidth="1"/>
     <col min="2" max="6" width="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="34" customHeight="1">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:6" ht="34" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="8"/>
@@ -2622,8 +2621,8 @@
       <c r="E1" s="8"/>
       <c r="F1" s="8"/>
     </row>
-    <row r="2" spans="1:6" ht="20" customHeight="1">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="8"/>
@@ -2632,12 +2631,12 @@
       <c r="E2" s="8"/>
       <c r="F2" s="8"/>
     </row>
-    <row r="4" spans="1:6" ht="16.5">
+    <row r="4" spans="1:6" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="58" customHeight="1">
+    <row r="5" spans="1:6" ht="58" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
         <v>3</v>
       </c>
@@ -2647,12 +2646,12 @@
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
     </row>
-    <row r="7" spans="1:6" ht="16.5">
+    <row r="7" spans="1:6" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="30" customHeight="1">
+    <row r="8" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
         <v>5</v>
       </c>
@@ -2662,7 +2661,7 @@
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
     </row>
-    <row r="9" spans="1:6" ht="56" customHeight="1">
+    <row r="9" spans="1:6" ht="56" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
         <v>6</v>
       </c>
@@ -2672,7 +2671,7 @@
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
     </row>
-    <row r="10" spans="1:6" ht="56" customHeight="1">
+    <row r="10" spans="1:6" ht="56" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
         <v>7</v>
       </c>
@@ -2682,7 +2681,7 @@
       <c r="E10" s="8"/>
       <c r="F10" s="8"/>
     </row>
-    <row r="11" spans="1:6" ht="56" customHeight="1">
+    <row r="11" spans="1:6" ht="56" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
         <v>8</v>
       </c>
@@ -2692,12 +2691,12 @@
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
     </row>
-    <row r="13" spans="1:6" ht="16.5">
+    <row r="13" spans="1:6" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="46" customHeight="1">
+    <row r="14" spans="1:6" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
         <v>10</v>
       </c>
@@ -2707,7 +2706,7 @@
       <c r="E14" s="8"/>
       <c r="F14" s="8"/>
     </row>
-    <row r="15" spans="1:6" ht="34" customHeight="1">
+    <row r="15" spans="1:6" ht="34" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
         <v>11</v>
       </c>
@@ -2717,7 +2716,7 @@
       <c r="E15" s="8"/>
       <c r="F15" s="8"/>
     </row>
-    <row r="16" spans="1:6" ht="40" customHeight="1">
+    <row r="16" spans="1:6" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
         <v>12</v>
       </c>
@@ -2727,7 +2726,7 @@
       <c r="E16" s="8"/>
       <c r="F16" s="8"/>
     </row>
-    <row r="17" spans="1:6" ht="46" customHeight="1">
+    <row r="17" spans="1:6" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
         <v>13</v>
       </c>
@@ -2737,7 +2736,7 @@
       <c r="E17" s="8"/>
       <c r="F17" s="8"/>
     </row>
-    <row r="18" spans="1:6" ht="40" customHeight="1">
+    <row r="18" spans="1:6" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
         <v>14</v>
       </c>
@@ -2747,12 +2746,12 @@
       <c r="E18" s="8"/>
       <c r="F18" s="8"/>
     </row>
-    <row r="20" spans="1:6" ht="16.5">
+    <row r="20" spans="1:6" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="40" customHeight="1">
+    <row r="21" spans="1:6" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
         <v>16</v>
       </c>
@@ -2762,7 +2761,7 @@
       <c r="E21" s="8"/>
       <c r="F21" s="8"/>
     </row>
-    <row r="22" spans="1:6" ht="34" customHeight="1">
+    <row r="22" spans="1:6" ht="34" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="9" t="s">
         <v>17</v>
       </c>
@@ -2772,7 +2771,7 @@
       <c r="E22" s="8"/>
       <c r="F22" s="8"/>
     </row>
-    <row r="23" spans="1:6" ht="34" customHeight="1">
+    <row r="23" spans="1:6" ht="34" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="9" t="s">
         <v>18</v>
       </c>
@@ -2810,7 +2809,7 @@
     <tabColor rgb="FF2E5395"/>
   </sheetPr>
   <dimension ref="A1:G49"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
@@ -2821,7 +2820,7 @@
     <col min="7" max="7" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30" customHeight="1">
+    <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>19</v>
       </c>
@@ -2844,7 +2843,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="22" customHeight="1">
+    <row r="2" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
         <v>26</v>
       </c>
@@ -2855,7 +2854,7 @@
       <c r="F2" s="12"/>
       <c r="G2" s="12"/>
     </row>
-    <row r="3" spans="1:7" ht="120" customHeight="1">
+    <row r="3" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>27</v>
       </c>
@@ -2878,7 +2877,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="120" customHeight="1">
+    <row r="4" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>27</v>
       </c>
@@ -2901,7 +2900,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="120" customHeight="1">
+    <row r="5" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>27</v>
       </c>
@@ -2924,7 +2923,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="120" customHeight="1">
+    <row r="6" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>27</v>
       </c>
@@ -2947,7 +2946,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="120" customHeight="1">
+    <row r="7" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>27</v>
       </c>
@@ -2970,7 +2969,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="22" customHeight="1">
+    <row r="8" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11" t="s">
         <v>58</v>
       </c>
@@ -2981,7 +2980,7 @@
       <c r="F8" s="12"/>
       <c r="G8" s="12"/>
     </row>
-    <row r="9" spans="1:7" ht="120" customHeight="1">
+    <row r="9" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>59</v>
       </c>
@@ -3004,7 +3003,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="120" customHeight="1">
+    <row r="10" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>59</v>
       </c>
@@ -3027,7 +3026,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="120" customHeight="1">
+    <row r="11" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>59</v>
       </c>
@@ -3050,7 +3049,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="120" customHeight="1">
+    <row r="12" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>59</v>
       </c>
@@ -3073,7 +3072,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="120" customHeight="1">
+    <row r="13" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>59</v>
       </c>
@@ -3096,7 +3095,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="22" customHeight="1">
+    <row r="14" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="11" t="s">
         <v>90</v>
       </c>
@@ -3107,7 +3106,7 @@
       <c r="F14" s="12"/>
       <c r="G14" s="12"/>
     </row>
-    <row r="15" spans="1:7" ht="120" customHeight="1">
+    <row r="15" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>91</v>
       </c>
@@ -3130,7 +3129,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="120" customHeight="1">
+    <row r="16" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>91</v>
       </c>
@@ -3153,7 +3152,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="120" customHeight="1">
+    <row r="17" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>91</v>
       </c>
@@ -3176,7 +3175,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="22" customHeight="1">
+    <row r="18" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="11" t="s">
         <v>110</v>
       </c>
@@ -3187,7 +3186,7 @@
       <c r="F18" s="12"/>
       <c r="G18" s="12"/>
     </row>
-    <row r="19" spans="1:7" ht="120" customHeight="1">
+    <row r="19" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>111</v>
       </c>
@@ -3210,7 +3209,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="120" customHeight="1">
+    <row r="20" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
         <v>111</v>
       </c>
@@ -3233,7 +3232,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="120" customHeight="1">
+    <row r="21" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>111</v>
       </c>
@@ -3256,7 +3255,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="120" customHeight="1">
+    <row r="22" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>111</v>
       </c>
@@ -3279,7 +3278,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="22" customHeight="1">
+    <row r="23" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="11" t="s">
         <v>136</v>
       </c>
@@ -3290,7 +3289,7 @@
       <c r="F23" s="12"/>
       <c r="G23" s="12"/>
     </row>
-    <row r="24" spans="1:7" ht="120" customHeight="1">
+    <row r="24" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
         <v>137</v>
       </c>
@@ -3313,7 +3312,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="120" customHeight="1">
+    <row r="25" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>137</v>
       </c>
@@ -3336,7 +3335,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="22" customHeight="1">
+    <row r="26" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="11" t="s">
         <v>150</v>
       </c>
@@ -3347,7 +3346,7 @@
       <c r="F26" s="12"/>
       <c r="G26" s="12"/>
     </row>
-    <row r="27" spans="1:7" ht="120" customHeight="1">
+    <row r="27" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
         <v>151</v>
       </c>
@@ -3370,7 +3369,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="120" customHeight="1">
+    <row r="28" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
         <v>151</v>
       </c>
@@ -3393,7 +3392,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="120" customHeight="1">
+    <row r="29" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
         <v>151</v>
       </c>
@@ -3416,7 +3415,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="22" customHeight="1">
+    <row r="30" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="11" t="s">
         <v>169</v>
       </c>
@@ -3427,7 +3426,7 @@
       <c r="F30" s="12"/>
       <c r="G30" s="12"/>
     </row>
-    <row r="31" spans="1:7" ht="120" customHeight="1">
+    <row r="31" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
         <v>170</v>
       </c>
@@ -3450,7 +3449,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="120" customHeight="1">
+    <row r="32" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
         <v>170</v>
       </c>
@@ -3473,7 +3472,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="120" customHeight="1">
+    <row r="33" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
         <v>170</v>
       </c>
@@ -3496,7 +3495,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="22" customHeight="1">
+    <row r="34" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="11" t="s">
         <v>188</v>
       </c>
@@ -3507,7 +3506,7 @@
       <c r="F34" s="12"/>
       <c r="G34" s="12"/>
     </row>
-    <row r="35" spans="1:7" ht="120" customHeight="1">
+    <row r="35" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
         <v>189</v>
       </c>
@@ -3530,7 +3529,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="120" customHeight="1">
+    <row r="36" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
         <v>189</v>
       </c>
@@ -3553,7 +3552,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="120" customHeight="1">
+    <row r="37" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
         <v>189</v>
       </c>
@@ -3576,7 +3575,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="22" customHeight="1">
+    <row r="38" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="11" t="s">
         <v>208</v>
       </c>
@@ -3587,7 +3586,7 @@
       <c r="F38" s="12"/>
       <c r="G38" s="12"/>
     </row>
-    <row r="39" spans="1:7" ht="120" customHeight="1">
+    <row r="39" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
         <v>209</v>
       </c>
@@ -3610,7 +3609,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="120" customHeight="1">
+    <row r="40" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
         <v>209</v>
       </c>
@@ -3633,7 +3632,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="120" customHeight="1">
+    <row r="41" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
         <v>209</v>
       </c>
@@ -3656,7 +3655,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="120" customHeight="1">
+    <row r="42" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
         <v>209</v>
       </c>
@@ -3679,7 +3678,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="120" customHeight="1">
+    <row r="43" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="3" t="s">
         <v>209</v>
       </c>
@@ -3702,7 +3701,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="120" customHeight="1">
+    <row r="44" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
         <v>209</v>
       </c>
@@ -3725,7 +3724,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="120" customHeight="1">
+    <row r="45" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
         <v>209</v>
       </c>
@@ -3748,7 +3747,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="22" customHeight="1">
+    <row r="46" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="11" t="s">
         <v>252</v>
       </c>
@@ -3759,7 +3758,7 @@
       <c r="F46" s="12"/>
       <c r="G46" s="12"/>
     </row>
-    <row r="47" spans="1:7" ht="120" customHeight="1">
+    <row r="47" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="3" t="s">
         <v>253</v>
       </c>
@@ -3782,7 +3781,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="120" customHeight="1">
+    <row r="48" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="3" t="s">
         <v>253</v>
       </c>
@@ -3805,7 +3804,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="120" customHeight="1">
+    <row r="49" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
         <v>253</v>
       </c>
@@ -3830,6 +3829,9 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A46:G46"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A30:G30"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A38:G38"/>
     <mergeCell ref="A23:G23"/>
@@ -3837,9 +3839,6 @@
     <mergeCell ref="A18:G18"/>
     <mergeCell ref="A8:G8"/>
     <mergeCell ref="A34:G34"/>
-    <mergeCell ref="A46:G46"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="A30:G30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3851,7 +3850,7 @@
     <tabColor rgb="FF9C6500"/>
   </sheetPr>
   <dimension ref="A1:J29"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8" style="4" customWidth="1"/>
     <col min="2" max="3" width="24" customWidth="1"/>
@@ -3863,7 +3862,7 @@
     <col min="10" max="10" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1">
+    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>272</v>
       </c>
@@ -3895,7 +3894,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="140" customHeight="1">
+    <row r="2" spans="1:10" ht="140" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>281</v>
       </c>
@@ -3923,7 +3922,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="140" customHeight="1">
+    <row r="3" spans="1:10" ht="140" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>289</v>
       </c>
@@ -3951,7 +3950,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="140" customHeight="1">
+    <row r="4" spans="1:10" ht="140" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>295</v>
       </c>
@@ -3977,7 +3976,7 @@
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
     </row>
-    <row r="5" spans="1:10" ht="140" customHeight="1">
+    <row r="5" spans="1:10" ht="140" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>300</v>
       </c>
@@ -4005,7 +4004,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="140" customHeight="1">
+    <row r="6" spans="1:10" ht="140" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>306</v>
       </c>
@@ -4031,7 +4030,7 @@
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
     </row>
-    <row r="7" spans="1:10" ht="140" customHeight="1">
+    <row r="7" spans="1:10" ht="140" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>310</v>
       </c>
@@ -4059,7 +4058,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="140" customHeight="1">
+    <row r="8" spans="1:10" ht="140" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>316</v>
       </c>
@@ -4087,7 +4086,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="140" customHeight="1">
+    <row r="9" spans="1:10" ht="140" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>323</v>
       </c>
@@ -4113,7 +4112,7 @@
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
     </row>
-    <row r="10" spans="1:10" ht="140" customHeight="1">
+    <row r="10" spans="1:10" ht="140" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>327</v>
       </c>
@@ -4139,7 +4138,7 @@
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
     </row>
-    <row r="11" spans="1:10" ht="140" customHeight="1">
+    <row r="11" spans="1:10" ht="140" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>333</v>
       </c>
@@ -4165,7 +4164,7 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
     </row>
-    <row r="12" spans="1:10" ht="140" customHeight="1">
+    <row r="12" spans="1:10" ht="140" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>339</v>
       </c>
@@ -4191,7 +4190,7 @@
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
     </row>
-    <row r="13" spans="1:10" ht="140" customHeight="1">
+    <row r="13" spans="1:10" ht="140" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>343</v>
       </c>
@@ -4217,7 +4216,7 @@
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
     </row>
-    <row r="14" spans="1:10" ht="140" customHeight="1">
+    <row r="14" spans="1:10" ht="140" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>348</v>
       </c>
@@ -4243,7 +4242,7 @@
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
     </row>
-    <row r="15" spans="1:10" ht="140" customHeight="1">
+    <row r="15" spans="1:10" ht="140" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>352</v>
       </c>
@@ -4271,7 +4270,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="140" customHeight="1">
+    <row r="16" spans="1:10" ht="140" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>360</v>
       </c>
@@ -4297,7 +4296,7 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
     </row>
-    <row r="17" spans="1:10" ht="140" customHeight="1">
+    <row r="17" spans="1:10" ht="140" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>365</v>
       </c>
@@ -4323,7 +4322,7 @@
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
     </row>
-    <row r="18" spans="1:10" ht="140" customHeight="1">
+    <row r="18" spans="1:10" ht="140" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>369</v>
       </c>
@@ -4349,7 +4348,7 @@
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
     </row>
-    <row r="19" spans="1:10" ht="140" customHeight="1">
+    <row r="19" spans="1:10" ht="140" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>373</v>
       </c>
@@ -4375,7 +4374,7 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
     </row>
-    <row r="20" spans="1:10" ht="140" customHeight="1">
+    <row r="20" spans="1:10" ht="140" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
         <v>377</v>
       </c>
@@ -4401,7 +4400,7 @@
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
     </row>
-    <row r="21" spans="1:10" ht="140" customHeight="1">
+    <row r="21" spans="1:10" ht="140" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>382</v>
       </c>
@@ -4427,7 +4426,7 @@
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
     </row>
-    <row r="22" spans="1:10" ht="140" customHeight="1">
+    <row r="22" spans="1:10" ht="140" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>386</v>
       </c>
@@ -4453,7 +4452,7 @@
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
     </row>
-    <row r="23" spans="1:10" ht="140" customHeight="1">
+    <row r="23" spans="1:10" ht="140" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>393</v>
       </c>
@@ -4479,7 +4478,7 @@
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
     </row>
-    <row r="24" spans="1:10" ht="140" customHeight="1">
+    <row r="24" spans="1:10" ht="140" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
         <v>399</v>
       </c>
@@ -4505,7 +4504,7 @@
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
     </row>
-    <row r="25" spans="1:10" ht="140" customHeight="1">
+    <row r="25" spans="1:10" ht="140" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>405</v>
       </c>
@@ -4531,7 +4530,7 @@
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
     </row>
-    <row r="26" spans="1:10" ht="140" customHeight="1">
+    <row r="26" spans="1:10" ht="140" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
         <v>411</v>
       </c>
@@ -4559,7 +4558,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="140" customHeight="1">
+    <row r="27" spans="1:10" ht="140" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
         <v>419</v>
       </c>
@@ -4587,7 +4586,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="140" customHeight="1">
+    <row r="28" spans="1:10" ht="140" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
         <v>427</v>
       </c>
@@ -4615,7 +4614,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="140" customHeight="1">
+    <row r="29" spans="1:10" ht="140" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
         <v>434</v>
       </c>
@@ -4659,7 +4658,7 @@
     <tabColor rgb="FF5B2C6F"/>
   </sheetPr>
   <dimension ref="A1:G42"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
@@ -4667,8 +4666,8 @@
     <col min="7" max="7" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30" customHeight="1">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="16" t="s">
         <v>442</v>
       </c>
       <c r="B1" s="8"/>
@@ -4678,12 +4677,12 @@
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
     </row>
-    <row r="3" spans="1:7" ht="15.5">
+    <row r="3" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="30" customHeight="1">
+    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>444</v>
       </c>
@@ -4703,7 +4702,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="120" customHeight="1">
+    <row r="5" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>450</v>
       </c>
@@ -4723,7 +4722,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="120" customHeight="1">
+    <row r="6" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>456</v>
       </c>
@@ -4743,7 +4742,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="120" customHeight="1">
+    <row r="7" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>462</v>
       </c>
@@ -4763,7 +4762,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="120" customHeight="1">
+    <row r="8" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>468</v>
       </c>
@@ -4783,7 +4782,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="120" customHeight="1">
+    <row r="9" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>474</v>
       </c>
@@ -4803,7 +4802,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="120" customHeight="1">
+    <row r="10" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>480</v>
       </c>
@@ -4823,7 +4822,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="120" customHeight="1">
+    <row r="11" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>486</v>
       </c>
@@ -4843,7 +4842,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="120" customHeight="1">
+    <row r="12" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>492</v>
       </c>
@@ -4863,12 +4862,12 @@
         <v>497</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="15.5">
+    <row r="14" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="90" customHeight="1">
+    <row r="15" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="17" t="s">
         <v>499</v>
       </c>
@@ -4878,21 +4877,21 @@
       <c r="E15" s="8"/>
       <c r="F15" s="8"/>
     </row>
-    <row r="16" spans="1:7" ht="60" customHeight="1">
-      <c r="A16" s="14"/>
+    <row r="16" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="15"/>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
       <c r="F16" s="8"/>
     </row>
-    <row r="18" spans="1:6" ht="15.5">
+    <row r="18" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="18" customHeight="1">
-      <c r="A19" s="16" t="s">
+    <row r="19" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="13" t="s">
         <v>501</v>
       </c>
       <c r="B19" s="8"/>
@@ -4901,8 +4900,8 @@
       <c r="E19" s="8"/>
       <c r="F19" s="8"/>
     </row>
-    <row r="20" spans="1:6" ht="56" customHeight="1">
-      <c r="A20" s="13" t="s">
+    <row r="20" spans="1:6" ht="56" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="14" t="s">
         <v>502</v>
       </c>
       <c r="B20" s="8"/>
@@ -4911,8 +4910,8 @@
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
     </row>
-    <row r="21" spans="1:6" ht="18" customHeight="1">
-      <c r="A21" s="16" t="s">
+    <row r="21" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="13" t="s">
         <v>503</v>
       </c>
       <c r="B21" s="8"/>
@@ -4921,8 +4920,8 @@
       <c r="E21" s="8"/>
       <c r="F21" s="8"/>
     </row>
-    <row r="22" spans="1:6" ht="56" customHeight="1">
-      <c r="A22" s="13" t="s">
+    <row r="22" spans="1:6" ht="56" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="14" t="s">
         <v>504</v>
       </c>
       <c r="B22" s="8"/>
@@ -4931,8 +4930,8 @@
       <c r="E22" s="8"/>
       <c r="F22" s="8"/>
     </row>
-    <row r="23" spans="1:6" ht="18" customHeight="1">
-      <c r="A23" s="16" t="s">
+    <row r="23" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="13" t="s">
         <v>505</v>
       </c>
       <c r="B23" s="8"/>
@@ -4941,8 +4940,8 @@
       <c r="E23" s="8"/>
       <c r="F23" s="8"/>
     </row>
-    <row r="24" spans="1:6" ht="56" customHeight="1">
-      <c r="A24" s="13" t="s">
+    <row r="24" spans="1:6" ht="56" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="14" t="s">
         <v>506</v>
       </c>
       <c r="B24" s="8"/>
@@ -4951,8 +4950,8 @@
       <c r="E24" s="8"/>
       <c r="F24" s="8"/>
     </row>
-    <row r="25" spans="1:6" ht="18" customHeight="1">
-      <c r="A25" s="16" t="s">
+    <row r="25" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="13" t="s">
         <v>507</v>
       </c>
       <c r="B25" s="8"/>
@@ -4961,8 +4960,8 @@
       <c r="E25" s="8"/>
       <c r="F25" s="8"/>
     </row>
-    <row r="26" spans="1:6" ht="56" customHeight="1">
-      <c r="A26" s="13" t="s">
+    <row r="26" spans="1:6" ht="56" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="14" t="s">
         <v>508</v>
       </c>
       <c r="B26" s="8"/>
@@ -4971,8 +4970,8 @@
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
     </row>
-    <row r="27" spans="1:6" ht="18" customHeight="1">
-      <c r="A27" s="16" t="s">
+    <row r="27" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="13" t="s">
         <v>509</v>
       </c>
       <c r="B27" s="8"/>
@@ -4981,8 +4980,8 @@
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
     </row>
-    <row r="28" spans="1:6" ht="56" customHeight="1">
-      <c r="A28" s="13" t="s">
+    <row r="28" spans="1:6" ht="56" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="14" t="s">
         <v>510</v>
       </c>
       <c r="B28" s="8"/>
@@ -4991,8 +4990,8 @@
       <c r="E28" s="8"/>
       <c r="F28" s="8"/>
     </row>
-    <row r="29" spans="1:6" ht="18" customHeight="1">
-      <c r="A29" s="16" t="s">
+    <row r="29" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="13" t="s">
         <v>511</v>
       </c>
       <c r="B29" s="8"/>
@@ -5001,8 +5000,8 @@
       <c r="E29" s="8"/>
       <c r="F29" s="8"/>
     </row>
-    <row r="30" spans="1:6" ht="56" customHeight="1">
-      <c r="A30" s="13" t="s">
+    <row r="30" spans="1:6" ht="56" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="14" t="s">
         <v>512</v>
       </c>
       <c r="B30" s="8"/>
@@ -5011,8 +5010,8 @@
       <c r="E30" s="8"/>
       <c r="F30" s="8"/>
     </row>
-    <row r="31" spans="1:6" ht="18" customHeight="1">
-      <c r="A31" s="16" t="s">
+    <row r="31" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="13" t="s">
         <v>513</v>
       </c>
       <c r="B31" s="8"/>
@@ -5021,8 +5020,8 @@
       <c r="E31" s="8"/>
       <c r="F31" s="8"/>
     </row>
-    <row r="32" spans="1:6" ht="56" customHeight="1">
-      <c r="A32" s="13" t="s">
+    <row r="32" spans="1:6" ht="56" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="14" t="s">
         <v>514</v>
       </c>
       <c r="B32" s="8"/>
@@ -5031,12 +5030,12 @@
       <c r="E32" s="8"/>
       <c r="F32" s="8"/>
     </row>
-    <row r="34" spans="1:7" ht="15.5">
+    <row r="34" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A34" s="5" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="30" customHeight="1">
+    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>516</v>
       </c>
@@ -5059,7 +5058,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="50" customHeight="1">
+    <row r="36" spans="1:7" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="6" t="s">
         <v>522</v>
       </c>
@@ -5076,7 +5075,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="50" customHeight="1">
+    <row r="37" spans="1:7" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="6" t="s">
         <v>525</v>
       </c>
@@ -5093,7 +5092,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="50" customHeight="1">
+    <row r="38" spans="1:7" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="6" t="s">
         <v>527</v>
       </c>
@@ -5108,7 +5107,7 @@
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
     </row>
-    <row r="39" spans="1:7" ht="50" customHeight="1">
+    <row r="39" spans="1:7" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="6" t="s">
         <v>529</v>
       </c>
@@ -5123,7 +5122,7 @@
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
     </row>
-    <row r="40" spans="1:7" ht="50" customHeight="1">
+    <row r="40" spans="1:7" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="6" t="s">
         <v>530</v>
       </c>
@@ -5140,7 +5139,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="50" customHeight="1">
+    <row r="41" spans="1:7" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="6" t="s">
         <v>533</v>
       </c>
@@ -5155,7 +5154,7 @@
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
     </row>
-    <row r="42" spans="1:7" ht="50" customHeight="1">
+    <row r="42" spans="1:7" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="6" t="s">
         <v>535</v>
       </c>
@@ -5174,14 +5173,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A25:F25"/>
-    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="A30:F30"/>
     <mergeCell ref="A1:G1"/>
@@ -5191,6 +5182,14 @@
     <mergeCell ref="A29:F29"/>
     <mergeCell ref="A27:F27"/>
     <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A24:F24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5202,7 +5201,7 @@
     <tabColor rgb="FF1E7B34"/>
   </sheetPr>
   <dimension ref="A1:E15"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -5210,8 +5209,8 @@
     <col min="4" max="5" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30" customHeight="1">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="16" t="s">
         <v>539</v>
       </c>
       <c r="B1" s="8"/>
@@ -5219,7 +5218,7 @@
       <c r="D1" s="8"/>
       <c r="E1" s="8"/>
     </row>
-    <row r="2" spans="1:5" ht="32" customHeight="1">
+    <row r="2" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="18" t="s">
         <v>540</v>
       </c>
@@ -5228,7 +5227,7 @@
       <c r="D2" s="8"/>
       <c r="E2" s="8"/>
     </row>
-    <row r="4" spans="1:5" ht="30" customHeight="1">
+    <row r="4" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>541</v>
       </c>
@@ -5245,7 +5244,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="135" customHeight="1">
+    <row r="5" spans="1:5" ht="135" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>546</v>
       </c>
@@ -5262,7 +5261,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="135" customHeight="1">
+    <row r="6" spans="1:5" ht="135" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>551</v>
       </c>
@@ -5279,7 +5278,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="135" customHeight="1">
+    <row r="7" spans="1:5" ht="135" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>556</v>
       </c>
@@ -5296,7 +5295,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="135" customHeight="1">
+    <row r="8" spans="1:5" ht="135" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>561</v>
       </c>
@@ -5313,7 +5312,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="135" customHeight="1">
+    <row r="9" spans="1:5" ht="135" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>566</v>
       </c>
@@ -5330,7 +5329,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="135" customHeight="1">
+    <row r="10" spans="1:5" ht="135" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>571</v>
       </c>
@@ -5347,7 +5346,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="135" customHeight="1">
+    <row r="11" spans="1:5" ht="135" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>576</v>
       </c>
@@ -5364,7 +5363,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="135" customHeight="1">
+    <row r="12" spans="1:5" ht="135" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>581</v>
       </c>
@@ -5381,7 +5380,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="135" customHeight="1">
+    <row r="13" spans="1:5" ht="135" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>586</v>
       </c>
@@ -5398,7 +5397,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="135" customHeight="1">
+    <row r="14" spans="1:5" ht="135" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>591</v>
       </c>
@@ -5415,7 +5414,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="135" customHeight="1">
+    <row r="15" spans="1:5" ht="135" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>596</v>
       </c>
@@ -5447,7 +5446,7 @@
     <tabColor rgb="FFC00000"/>
   </sheetPr>
   <dimension ref="A1:G15"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="3" width="38" customWidth="1"/>
@@ -5456,8 +5455,8 @@
     <col min="7" max="7" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30" customHeight="1">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="16" t="s">
         <v>601</v>
       </c>
       <c r="B1" s="8"/>
@@ -5466,7 +5465,7 @@
       <c r="E1" s="8"/>
       <c r="F1" s="8"/>
     </row>
-    <row r="2" spans="1:7" ht="40" customHeight="1">
+    <row r="2" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="18" t="s">
         <v>602</v>
       </c>
@@ -5476,7 +5475,7 @@
       <c r="E2" s="8"/>
       <c r="F2" s="8"/>
     </row>
-    <row r="4" spans="1:7" ht="30" customHeight="1">
+    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>19</v>
       </c>
@@ -5499,7 +5498,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="175" customHeight="1">
+    <row r="5" spans="1:7" ht="175" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>609</v>
       </c>
@@ -5522,7 +5521,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="175" customHeight="1">
+    <row r="6" spans="1:7" ht="175" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>616</v>
       </c>
@@ -5545,7 +5544,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="175" customHeight="1">
+    <row r="7" spans="1:7" ht="175" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>623</v>
       </c>
@@ -5568,7 +5567,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="175" customHeight="1">
+    <row r="8" spans="1:7" ht="175" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>630</v>
       </c>
@@ -5591,7 +5590,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="175" customHeight="1">
+    <row r="9" spans="1:7" ht="175" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>637</v>
       </c>
@@ -5614,7 +5613,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="175" customHeight="1">
+    <row r="10" spans="1:7" ht="175" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>644</v>
       </c>
@@ -5637,7 +5636,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="175" customHeight="1">
+    <row r="11" spans="1:7" ht="175" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>651</v>
       </c>
@@ -5660,7 +5659,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="175" customHeight="1">
+    <row r="12" spans="1:7" ht="175" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>657</v>
       </c>
@@ -5683,7 +5682,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="175" customHeight="1">
+    <row r="13" spans="1:7" ht="175" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>664</v>
       </c>
@@ -5706,7 +5705,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="175" customHeight="1">
+    <row r="14" spans="1:7" ht="175" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>671</v>
       </c>
@@ -5729,7 +5728,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="175" customHeight="1">
+    <row r="15" spans="1:7" ht="175" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>678</v>
       </c>
